--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 5.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 5.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Keuangan 5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D8507-3C5C-4E96-B443-42081C5A7059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -193,8 +192,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -311,7 +311,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,26 +336,28 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Comma 2" xfId="2"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 2" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -641,7 +643,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67762719-8795-4013-A5E4-7A17415A5304}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -666,14 +668,14 @@
       <c r="B1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="15" t="s">
+      <c r="D1" s="12"/>
+      <c r="E1" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="15"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="2:11" s="2" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
@@ -884,12 +886,12 @@
       <c r="K13" s="5"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="H15" s="10" t="s">
         <v>42</v>
       </c>
@@ -898,11 +900,11 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
       <c r="H16" s="9" t="s">
         <v>43</v>
       </c>
@@ -914,11 +916,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
       <c r="H17" s="5" t="s">
         <v>45</v>
       </c>
@@ -930,11 +932,12 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="F18" s="17"/>
       <c r="H18" s="5" t="s">
         <v>46</v>
       </c>
@@ -946,11 +949,12 @@
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="F19" s="16"/>
       <c r="H19" s="5" t="s">
         <v>47</v>
       </c>
@@ -962,6 +966,7 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="F20" s="16"/>
       <c r="H20" s="5" t="s">
         <v>48</v>
       </c>
@@ -973,150 +978,151 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="12" t="s">
+      <c r="B33" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="12"/>
+      <c r="C33" s="15"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="12"/>
+      <c r="C37" s="15"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="12" t="s">
+      <c r="B42" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="12"/>
+      <c r="C42" s="15"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
     </row>
   </sheetData>
+  <sortState ref="F18:F23">
+    <sortCondition ref="F18:F23"/>
+  </sortState>
   <mergeCells count="25">
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B38:E38"/>
@@ -1131,6 +1137,11 @@
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:H34"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:D16"/>
@@ -1139,7 +1150,7 @@
     <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1" xr:uid="{D7814D8C-3515-4771-AEA6-D311089E22AD}"/>
+    <hyperlink ref="E1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 5.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 5.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Keuangan 5\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{304D8507-3C5C-4E96-B443-42081C5A7059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="8" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -192,9 +193,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -311,7 +311,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -336,28 +336,26 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Comma 2" xfId="2"/>
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Hyperlink" xfId="5" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -643,7 +641,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67762719-8795-4013-A5E4-7A17415A5304}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -668,14 +666,14 @@
       <c r="B1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="12"/>
-      <c r="E1" s="13" t="s">
+      <c r="D1" s="14"/>
+      <c r="E1" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="F1" s="13"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="2:11" s="2" customFormat="1" ht="33" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
@@ -886,12 +884,12 @@
       <c r="K13" s="5"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
       <c r="H15" s="10" t="s">
         <v>42</v>
       </c>
@@ -900,11 +898,11 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
       <c r="H16" s="9" t="s">
         <v>43</v>
       </c>
@@ -916,11 +914,11 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
       <c r="H17" s="5" t="s">
         <v>45</v>
       </c>
@@ -932,12 +930,11 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="F18" s="17"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
       <c r="H18" s="5" t="s">
         <v>46</v>
       </c>
@@ -949,12 +946,11 @@
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="F19" s="16"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
       <c r="H19" s="5" t="s">
         <v>47</v>
       </c>
@@ -966,7 +962,6 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="F20" s="16"/>
       <c r="H20" s="5" t="s">
         <v>48</v>
       </c>
@@ -978,151 +973,150 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="16"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="F22" s="16"/>
+      <c r="C22" s="13"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="14"/>
-      <c r="F23" s="16"/>
+      <c r="C23" s="13"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="14" t="s">
+      <c r="B27" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="15" t="s">
+      <c r="B33" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C33" s="15"/>
+      <c r="C33" s="12"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="14" t="s">
+      <c r="B35" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="15"/>
+      <c r="C37" s="12"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="15" t="s">
+      <c r="B42" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="15"/>
+      <c r="C42" s="12"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
     </row>
   </sheetData>
-  <sortState ref="F18:F23">
-    <sortCondition ref="F18:F23"/>
-  </sortState>
   <mergeCells count="25">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B38:E38"/>
@@ -1137,11 +1131,6 @@
     <mergeCell ref="B35:G35"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B34:H34"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="B15:E15"/>
     <mergeCell ref="B16:D16"/>
@@ -1150,7 +1139,7 @@
     <mergeCell ref="B19:D19"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E1" r:id="rId1"/>
+    <hyperlink ref="E1" r:id="rId1" xr:uid="{D7814D8C-3515-4771-AEA6-D311089E22AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
